--- a/Outputs/Scenarios/PtX_demand_SK_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SK_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001396519609567323</v>
       </c>
       <c r="K16" t="n">
-        <v>3.084607230385784e-05</v>
+        <v>7.197416870900164e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>5.141012050642974e-05</v>
+        <v>2.15922506127005e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1333,7 +1333,7 @@
         <v>0.0001119173419487328</v>
       </c>
       <c r="K24" t="n">
-        <v>5.654570615363557e-05</v>
+        <v>5.654570615363558e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0006774359062697156</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0004042626442032225</v>
+        <v>0.0004042626442032226</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>2.012148366262912e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>2.05640482025719e-05</v>
+        <v>9.253821691157357e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0020673772607307</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0001544367736555476</v>
+        <v>0.0003603524718629444</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.000257394622759246</v>
+        <v>0.0001081057415588833</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0001088093295121421</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0001029578491036984</v>
+        <v>4.63310320966643e-05</v>
       </c>
     </row>
     <row r="43">
